--- a/Backend/public/docs/ventas-credito-fiscal-format.xlsx
+++ b/Backend/public/docs/ventas-credito-fiscal-format.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
   <si>
     <t>nombre_comercial</t>
   </si>
@@ -138,6 +138,9 @@
     <t>- Las filas se agruparán en ventas según el cliente y la fecha.</t>
   </si>
   <si>
+    <t>- Utilice las listas desplegables para seleccionar valores en tipo de documento, tipo de ítem, forma de pago y condición.</t>
+  </si>
+  <si>
     <t>2. CAMPOS OBLIGATORIOS:</t>
   </si>
   <si>
@@ -180,7 +183,7 @@
     <t>5. FORMAS DE PAGO:</t>
   </si>
   <si>
-    <t>- Efectivo, Tarjeta, Cheque, Transferencia, Crédito, etc.</t>
+    <t>- Efectivo, Tarjeta de crédito/débito, Cheque, Transferencia, CARGO AUTOMATICO.</t>
   </si>
   <si>
     <t>6. CONDICIÓN:</t>
@@ -730,6 +733,26 @@
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
+  <dataValidations count="6">
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M2:M101">
+      <formula1>"Producto,Servicio"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N2:N101">
+      <formula1>"Efectivo,Tarjeta de crédito/débito,Cheque,Transferencia,CARGO AUTOMATICO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V2:V101">
+      <formula1>"Contado,Crédito"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M2">
+      <formula1>"Producto,Servicio"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N2">
+      <formula1>"Efectivo,Tarjeta de crédito/débito,Cheque,Transferencia,CARGO AUTOMATICO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V2">
+      <formula1>"Contado,Crédito"</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
@@ -750,7 +773,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true" style="0"/>
@@ -782,13 +805,13 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
     </row>
@@ -817,13 +840,13 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" t="s">
+      <c r="A17" s="1" t="s">
         <v>48</v>
       </c>
     </row>
@@ -832,13 +855,13 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" t="s">
+      <c r="A21" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -847,29 +870,34 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" t="s">
+      <c r="A25" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/Backend/public/docs/ventas-credito-fiscal-format.xlsx
+++ b/Backend/public/docs/ventas-credito-fiscal-format.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47">
   <si>
     <t>nombre_comercial</t>
   </si>
@@ -85,42 +85,6 @@
   </si>
   <si>
     <t>fecha_pago</t>
-  </si>
-  <si>
-    <t>Empresa ABC</t>
-  </si>
-  <si>
-    <t>Corporación ABC S.A. de C.V.</t>
-  </si>
-  <si>
-    <t>0614-010190-101-0</t>
-  </si>
-  <si>
-    <t>12345-6</t>
-  </si>
-  <si>
-    <t>1a Calle Poniente #123, Colonia Centro</t>
-  </si>
-  <si>
-    <t>2222-3333</t>
-  </si>
-  <si>
-    <t>info@empresa-abc.com</t>
-  </si>
-  <si>
-    <t>2025-03-25</t>
-  </si>
-  <si>
-    <t>Servicio de mantenimiento</t>
-  </si>
-  <si>
-    <t>Servicio</t>
-  </si>
-  <si>
-    <t>Tarjeta de crédito/débito</t>
-  </si>
-  <si>
-    <t>Contado</t>
   </si>
   <si>
     <t>INSTRUCCIONES PARA IMPORTAR VENTAS (CRÉDITO FISCAL)</t>
@@ -565,19 +529,19 @@
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="34" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="21" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="9" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="8" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="4" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="4" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="10" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="19" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="16" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="45" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="11" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="12" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="30" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="11" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="10" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="8" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="6" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="13" bestFit="true" customWidth="true" style="0"/>
     <col min="13" max="13" width="11" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="30" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="12" bestFit="true" customWidth="true" style="0"/>
     <col min="15" max="15" width="11" bestFit="true" customWidth="true" style="0"/>
     <col min="16" max="16" width="8" bestFit="true" customWidth="true" style="0"/>
     <col min="17" max="17" width="9" bestFit="true" customWidth="true" style="0"/>
@@ -661,93 +625,27 @@
       </c>
     </row>
     <row r="2" spans="1:23">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2">
-        <v>12345</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>100.0</v>
-      </c>
-      <c r="R2">
-        <v>100.0</v>
-      </c>
-      <c r="S2">
-        <v>13.0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>113.0</v>
-      </c>
-      <c r="V2" t="s">
-        <v>34</v>
-      </c>
-      <c r="W2" t="s">
-        <v>30</v>
-      </c>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="V2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
   <dataValidations count="6">
     <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M2:M101">
-      <formula1>"Producto,Servicio"</formula1>
+      <formula1>"Servicio"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N2:N101">
-      <formula1>"Efectivo,Tarjeta de crédito/débito,Cheque,Transferencia,CARGO AUTOMATICO"</formula1>
+      <formula1>"Tarjeta de crédito/débito"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V2:V101">
       <formula1>"Contado,Crédito"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M2">
-      <formula1>"Producto,Servicio"</formula1>
+      <formula1>"Servicio"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N2">
-      <formula1>"Efectivo,Tarjeta de crédito/débito,Cheque,Transferencia,CARGO AUTOMATICO"</formula1>
+      <formula1>"Tarjeta de crédito/débito"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V2">
       <formula1>"Contado,Crédito"</formula1>
@@ -782,122 +680,122 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="3" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Backend/public/docs/ventas-credito-fiscal-format.xlsx
+++ b/Backend/public/docs/ventas-credito-fiscal-format.xlsx
@@ -129,10 +129,10 @@
     <t>3. CÓDIGOS DE DEPARTAMENTOS Y MUNICIPIOS:</t>
   </si>
   <si>
-    <t>- Los códigos de departamento deben corresponder a los registrados en el sistema (ej. 01 para San Salvador).</t>
-  </si>
-  <si>
-    <t>- Los códigos de municipio deben corresponder a los registrados en el sistema (ej. 0101 para San Salvador).</t>
+    <t>- Los códigos de departamento deben corresponder a los registrados en el sistema (ej. 6 para San Salvador).</t>
+  </si>
+  <si>
+    <t>- Los códigos de municipio deben corresponder a los registrados en el sistema (ej. 24 para San Salvador).</t>
   </si>
   <si>
     <t>4. TIPOS DE ÍTEM:</t>
@@ -147,7 +147,7 @@
     <t>5. FORMAS DE PAGO:</t>
   </si>
   <si>
-    <t>- Efectivo, Tarjeta de crédito/débito, Cheque, Transferencia, CARGO AUTOMATICO.</t>
+    <t>- Efectivo, Tarjeta de crédito/débito</t>
   </si>
   <si>
     <t>6. CONDICIÓN:</t>

--- a/Backend/public/docs/ventas-credito-fiscal-format.xlsx
+++ b/Backend/public/docs/ventas-credito-fiscal-format.xlsx
@@ -5,20 +5,19 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseespana/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseespana/Documents/GitHub/SP/smartpyme/Backend/public/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B00899-5D08-5147-B122-81FB3DA93BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{649A1D04-3E93-5F4F-AE62-846BD998943D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plantila ventas credito Fiscal" sheetId="1" r:id="rId1"/>
-    <sheet name="Valores" sheetId="3" r:id="rId2"/>
+    <sheet name="Valores" sheetId="3" state="hidden" r:id="rId2"/>
     <sheet name="Instrucciones" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
